--- a/MU/BRD - test Doc/MU user manual infoneo (2).xlsx
+++ b/MU/BRD - test Doc/MU user manual infoneo (2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="24000" windowHeight="9600" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Flow" sheetId="1" r:id="rId1"/>
@@ -2936,7 +2936,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3034,15 +3034,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -3055,15 +3046,9 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -3091,9 +3076,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -3103,12 +3085,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="182" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3126,9 +3102,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
@@ -3741,53 +3714,53 @@
   <dimension ref="A1:Z71"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7142857142857" style="69" customWidth="1"/>
+    <col min="1" max="1" width="22.7142857142857" style="61" customWidth="1"/>
     <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="49.8571428571429" style="70" customWidth="1"/>
+    <col min="3" max="3" width="49.8571428571429" style="48" customWidth="1"/>
     <col min="4" max="4" width="46.8571428571429" customWidth="1"/>
     <col min="5" max="5" width="57.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:26">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="72" t="s">
+      <c r="C1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="72" t="s">
+      <c r="D1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="72" t="s">
+      <c r="E1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
-      <c r="R1" s="73"/>
-      <c r="S1" s="73"/>
-      <c r="T1" s="73"/>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73"/>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
+      <c r="Z1" s="64"/>
     </row>
     <row r="2" ht="135" spans="1:26">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="65" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -3796,7 +3769,7 @@
       <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="66" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -3804,20 +3777,20 @@
       </c>
     </row>
     <row r="3" ht="75" spans="1:26">
-      <c r="A3" s="76"/>
+      <c r="A3" s="67"/>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="66" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" ht="75" spans="1:26">
-      <c r="A4" s="76"/>
+      <c r="A4" s="67"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -3830,14 +3803,14 @@
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="77"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
+      <c r="A5" s="68"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
     </row>
     <row r="6" ht="75" spans="1:26">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="67" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -3846,7 +3819,7 @@
       <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="80" t="s">
+      <c r="D6" s="71" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -3854,7 +3827,7 @@
       </c>
     </row>
     <row r="7" ht="75" spans="1:26">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="67" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -3863,37 +3836,37 @@
       <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="75" t="s">
+      <c r="D7" s="66" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" ht="56" customHeight="1" spans="1:26">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="67" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="75" t="s">
+      <c r="C8" s="66" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
     <row r="9" ht="60" spans="1:26">
-      <c r="A9" s="76"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="75" t="s">
+      <c r="C9" s="66" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
     <row r="10" ht="60" spans="1:26">
-      <c r="A10" s="76" t="s">
+      <c r="A10" s="67" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -3902,13 +3875,13 @@
       <c r="C10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="80" t="s">
+      <c r="D10" s="71" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" customFormat="1" ht="60" spans="1:26">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="67" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -3923,31 +3896,31 @@
       <c r="E11" s="3"/>
     </row>
     <row r="12" customFormat="1" ht="45" spans="1:26">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="67" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="75" t="s">
+      <c r="C12" s="66" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
     <row r="13" customFormat="1" ht="60" spans="1:26">
-      <c r="A13" s="76"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="66" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
     <row r="14" customFormat="1" ht="60" spans="1:26">
-      <c r="A14" s="76" t="s">
+      <c r="A14" s="67" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -3962,7 +3935,7 @@
       <c r="E14" s="3"/>
     </row>
     <row r="15" ht="60" spans="1:26">
-      <c r="A15" s="76" t="s">
+      <c r="A15" s="67" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3971,37 +3944,37 @@
       <c r="C15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="66" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" ht="45" spans="1:26">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="67" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="75" t="s">
+      <c r="C16" s="66" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
     </row>
     <row r="17" ht="60" spans="1:5">
-      <c r="A17" s="76"/>
+      <c r="A17" s="67"/>
       <c r="B17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="75" t="s">
+      <c r="C17" s="66" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
     <row r="18" customFormat="1" ht="60" spans="1:5">
-      <c r="A18" s="76" t="s">
+      <c r="A18" s="67" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -4014,7 +3987,7 @@
       <c r="E18" s="3"/>
     </row>
     <row r="19" ht="60" spans="1:5">
-      <c r="A19" s="76" t="s">
+      <c r="A19" s="67" t="s">
         <v>40</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -4023,50 +3996,50 @@
       <c r="C19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="66" t="s">
         <v>42</v>
       </c>
       <c r="E19" s="3"/>
     </row>
     <row r="20" ht="45" spans="1:5">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="67" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="75" t="s">
+      <c r="C20" s="66" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
     <row r="21" ht="60" spans="1:5">
-      <c r="A21" s="76"/>
+      <c r="A21" s="67"/>
       <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="75" t="s">
+      <c r="C21" s="66" t="s">
         <v>25</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
     <row r="22" ht="90" spans="1:5">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="67" t="s">
         <v>43</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="75" t="s">
+      <c r="C22" s="66" t="s">
         <v>45</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
     <row r="23" ht="65" customHeight="1" spans="1:5">
-      <c r="A23" s="76" t="s">
+      <c r="A23" s="67" t="s">
         <v>46</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -4075,7 +4048,7 @@
       <c r="C23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="80" t="s">
+      <c r="D23" s="71" t="s">
         <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -4083,7 +4056,7 @@
       </c>
     </row>
     <row r="24" ht="65" customHeight="1" spans="1:5">
-      <c r="A24" s="76" t="s">
+      <c r="A24" s="67" t="s">
         <v>51</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -4092,74 +4065,74 @@
       <c r="C24" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="80" t="s">
+      <c r="D24" s="71" t="s">
         <v>49</v>
       </c>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" s="66" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A25" s="81" t="s">
+    <row r="25" s="58" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A25" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="82"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="82"/>
-      <c r="E25" s="83"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="74"/>
     </row>
     <row r="26" ht="90" spans="1:5">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="60" t="s">
+      <c r="B26" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="85" t="s">
+      <c r="C26" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="85" t="s">
+      <c r="D26" s="76" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="60"/>
+      <c r="E26" s="54"/>
     </row>
     <row r="27" ht="45" spans="1:5">
-      <c r="A27" s="84"/>
+      <c r="A27" s="75"/>
       <c r="B27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="75" t="s">
+      <c r="C27" s="66" t="s">
         <v>58</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
     <row r="28" ht="60" spans="1:5">
-      <c r="A28" s="86"/>
+      <c r="A28" s="77"/>
       <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="75" t="s">
+      <c r="C28" s="66" t="s">
         <v>59</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
     <row r="29" ht="75" spans="1:5">
-      <c r="A29" s="76" t="s">
+      <c r="A29" s="67" t="s">
         <v>60</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="75" t="s">
+      <c r="C29" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="87" t="s">
+      <c r="D29" s="78" t="s">
         <v>62</v>
       </c>
       <c r="E29" s="3"/>
     </row>
     <row r="30" ht="45" spans="1:5">
-      <c r="A30" s="76" t="s">
+      <c r="A30" s="67" t="s">
         <v>63</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -4172,7 +4145,7 @@
       <c r="E30" s="3"/>
     </row>
     <row r="31" ht="55" customHeight="1" spans="1:5">
-      <c r="A31" s="76" t="s">
+      <c r="A31" s="67" t="s">
         <v>65</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -4194,7 +4167,7 @@
       <c r="C32" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="75"/>
+      <c r="D32" s="66"/>
       <c r="E32" s="3"/>
     </row>
     <row r="33" ht="45" spans="1:5">
@@ -4205,7 +4178,7 @@
       <c r="C33" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="75"/>
+      <c r="D33" s="66"/>
       <c r="E33" s="3"/>
     </row>
     <row r="34" ht="45" spans="1:5">
@@ -4213,10 +4186,10 @@
       <c r="B34" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="75" t="s">
+      <c r="C34" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="75"/>
+      <c r="D34" s="66"/>
       <c r="E34" s="3"/>
     </row>
     <row r="35" ht="75" spans="1:5">
@@ -4226,10 +4199,10 @@
       <c r="B35" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="75" t="s">
+      <c r="C35" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="75" t="s">
+      <c r="D35" s="66" t="s">
         <v>73</v>
       </c>
       <c r="E35" s="3"/>
@@ -4239,7 +4212,7 @@
       <c r="B36" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="75" t="s">
+      <c r="C36" s="66" t="s">
         <v>75</v>
       </c>
       <c r="D36" s="3"/>
@@ -4250,98 +4223,98 @@
       <c r="B37" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="75" t="s">
+      <c r="C37" s="66" t="s">
         <v>76</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
     <row r="38" ht="60" spans="1:5">
-      <c r="A38" s="88" t="s">
+      <c r="A38" s="79" t="s">
         <v>77</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="75" t="s">
+      <c r="C38" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="75"/>
+      <c r="D38" s="66"/>
       <c r="E38" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" ht="60" spans="1:5">
-      <c r="A39" s="84"/>
+      <c r="A39" s="75"/>
       <c r="B39" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="75" t="s">
+      <c r="C39" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="75"/>
+      <c r="D39" s="66"/>
       <c r="E39" s="3"/>
     </row>
     <row r="40" ht="90" spans="1:5">
-      <c r="A40" s="88" t="s">
+      <c r="A40" s="79" t="s">
         <v>81</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="75" t="s">
+      <c r="C40" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="75" t="s">
+      <c r="D40" s="66" t="s">
         <v>83</v>
       </c>
       <c r="E40" s="3"/>
     </row>
     <row r="41" ht="75" spans="1:5">
-      <c r="A41" s="84"/>
+      <c r="A41" s="75"/>
       <c r="B41" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="75" t="s">
+      <c r="C41" s="66" t="s">
         <v>75</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
     <row r="42" ht="45" spans="1:5">
-      <c r="A42" s="86"/>
+      <c r="A42" s="77"/>
       <c r="B42" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="75" t="s">
+      <c r="C42" s="66" t="s">
         <v>76</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
     <row r="43" ht="75" spans="1:5">
-      <c r="A43" s="76" t="s">
+      <c r="A43" s="67" t="s">
         <v>84</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="75" t="s">
+      <c r="C43" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="87" t="s">
+      <c r="D43" s="78" t="s">
         <v>85</v>
       </c>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" s="67" customFormat="1" ht="45" spans="1:5">
-      <c r="A44" s="74" t="s">
+    <row r="44" s="59" customFormat="1" ht="45" spans="1:5">
+      <c r="A44" s="65" t="s">
         <v>86</v>
       </c>
       <c r="B44" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="89" t="s">
+      <c r="C44" s="80" t="s">
         <v>87</v>
       </c>
       <c r="D44" s="22" t="s">
@@ -4356,10 +4329,10 @@
       <c r="B45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="75" t="s">
+      <c r="C45" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="75" t="s">
+      <c r="D45" s="66" t="s">
         <v>90</v>
       </c>
       <c r="E45" s="3"/>
@@ -4369,7 +4342,7 @@
       <c r="B46" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="75" t="s">
+      <c r="C46" s="66" t="s">
         <v>75</v>
       </c>
       <c r="D46" s="3"/>
@@ -4380,7 +4353,7 @@
       <c r="B47" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="75" t="s">
+      <c r="C47" s="66" t="s">
         <v>76</v>
       </c>
       <c r="D47" s="3"/>
@@ -4393,10 +4366,10 @@
       <c r="B48" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="75" t="s">
+      <c r="C48" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="D48" s="75"/>
+      <c r="D48" s="66"/>
       <c r="E48" s="3" t="s">
         <v>79</v>
       </c>
@@ -4406,72 +4379,72 @@
       <c r="B49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="75" t="s">
+      <c r="C49" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="D49" s="75"/>
+      <c r="D49" s="66"/>
       <c r="E49" s="3"/>
     </row>
     <row r="50" ht="90" spans="1:5">
-      <c r="A50" s="88" t="s">
+      <c r="A50" s="79" t="s">
         <v>91</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="75" t="s">
+      <c r="C50" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="75" t="s">
+      <c r="D50" s="66" t="s">
         <v>92</v>
       </c>
       <c r="E50" s="3"/>
     </row>
     <row r="51" ht="75" spans="1:5">
-      <c r="A51" s="84"/>
+      <c r="A51" s="75"/>
       <c r="B51" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="75" t="s">
+      <c r="C51" s="66" t="s">
         <v>75</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
     </row>
     <row r="52" ht="45" spans="1:5">
-      <c r="A52" s="86"/>
+      <c r="A52" s="77"/>
       <c r="B52" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="75" t="s">
+      <c r="C52" s="66" t="s">
         <v>76</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
     </row>
     <row r="53" ht="75" spans="1:5">
-      <c r="A53" s="76" t="s">
+      <c r="A53" s="67" t="s">
         <v>93</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="75" t="s">
+      <c r="C53" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="87" t="s">
+      <c r="D53" s="78" t="s">
         <v>85</v>
       </c>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" s="67" customFormat="1" ht="45" spans="1:5">
-      <c r="A54" s="74" t="s">
+    <row r="54" s="59" customFormat="1" ht="45" spans="1:5">
+      <c r="A54" s="65" t="s">
         <v>94</v>
       </c>
       <c r="B54" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="89" t="s">
+      <c r="C54" s="80" t="s">
         <v>95</v>
       </c>
       <c r="D54" s="22" t="s">
@@ -4486,10 +4459,10 @@
       <c r="B56" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="75" t="s">
+      <c r="C56" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="75" t="s">
+      <c r="D56" s="66" t="s">
         <v>97</v>
       </c>
       <c r="E56" s="3"/>
@@ -4499,7 +4472,7 @@
       <c r="B57" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="75" t="s">
+      <c r="C57" s="66" t="s">
         <v>75</v>
       </c>
       <c r="D57" s="3"/>
@@ -4510,7 +4483,7 @@
       <c r="B58" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="75" t="s">
+      <c r="C58" s="66" t="s">
         <v>76</v>
       </c>
       <c r="D58" s="3"/>
@@ -4523,10 +4496,10 @@
       <c r="B59" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="75" t="s">
+      <c r="C59" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="D59" s="75"/>
+      <c r="D59" s="66"/>
       <c r="E59" s="3" t="s">
         <v>79</v>
       </c>
@@ -4536,72 +4509,72 @@
       <c r="B60" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="75" t="s">
+      <c r="C60" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="75"/>
+      <c r="D60" s="66"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" s="68" customFormat="1" ht="90" spans="1:5">
-      <c r="A61" s="90" t="s">
+    <row r="61" s="60" customFormat="1" ht="90" spans="1:5">
+      <c r="A61" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="91" t="s">
+      <c r="B61" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="92" t="s">
+      <c r="C61" s="83" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="92" t="s">
+      <c r="D61" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="E61" s="91"/>
-    </row>
-    <row r="62" s="68" customFormat="1" ht="75" spans="1:5">
-      <c r="A62" s="93"/>
-      <c r="B62" s="91" t="s">
+      <c r="E61" s="82"/>
+    </row>
+    <row r="62" s="60" customFormat="1" ht="75" spans="1:5">
+      <c r="A62" s="84"/>
+      <c r="B62" s="82" t="s">
         <v>74</v>
       </c>
-      <c r="C62" s="92" t="s">
+      <c r="C62" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="D62" s="91"/>
-      <c r="E62" s="91"/>
-    </row>
-    <row r="63" s="68" customFormat="1" ht="45" spans="1:5">
-      <c r="A63" s="94"/>
-      <c r="B63" s="91" t="s">
+      <c r="D62" s="82"/>
+      <c r="E62" s="82"/>
+    </row>
+    <row r="63" s="60" customFormat="1" ht="45" spans="1:5">
+      <c r="A63" s="85"/>
+      <c r="B63" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="92" t="s">
+      <c r="C63" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="D63" s="91"/>
-      <c r="E63" s="91"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="82"/>
     </row>
     <row r="64" ht="75" spans="1:5">
-      <c r="A64" s="76" t="s">
+      <c r="A64" s="67" t="s">
         <v>98</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C64" s="75" t="s">
+      <c r="C64" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="D64" s="87" t="s">
+      <c r="D64" s="78" t="s">
         <v>85</v>
       </c>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" s="67" customFormat="1" ht="45" spans="1:5">
-      <c r="A65" s="74" t="s">
+    <row r="65" s="59" customFormat="1" ht="45" spans="1:5">
+      <c r="A65" s="65" t="s">
         <v>94</v>
       </c>
       <c r="B65" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C65" s="89" t="s">
+      <c r="C65" s="80" t="s">
         <v>95</v>
       </c>
       <c r="D65" s="22" t="s">
@@ -4609,69 +4582,69 @@
       </c>
       <c r="E65" s="22"/>
     </row>
-    <row r="66" s="66" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A66" s="95" t="s">
+    <row r="66" s="58" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A66" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="B66" s="95"/>
-      <c r="C66" s="95"/>
-      <c r="D66" s="95"/>
-      <c r="E66" s="95"/>
+      <c r="B66" s="86"/>
+      <c r="C66" s="86"/>
+      <c r="D66" s="86"/>
+      <c r="E66" s="86"/>
     </row>
     <row r="67" ht="90" spans="1:5">
-      <c r="A67" s="84" t="s">
+      <c r="A67" s="75" t="s">
         <v>100</v>
       </c>
-      <c r="B67" s="60" t="s">
+      <c r="B67" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C67" s="85" t="s">
+      <c r="C67" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="85" t="s">
+      <c r="D67" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="E67" s="60"/>
+      <c r="E67" s="54"/>
     </row>
     <row r="68" ht="45" spans="1:5">
-      <c r="A68" s="84"/>
+      <c r="A68" s="75"/>
       <c r="B68" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="75" t="s">
+      <c r="C68" s="66" t="s">
         <v>58</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
     </row>
     <row r="69" ht="60" spans="1:5">
-      <c r="A69" s="86"/>
+      <c r="A69" s="77"/>
       <c r="B69" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C69" s="75" t="s">
+      <c r="C69" s="66" t="s">
         <v>59</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
     </row>
     <row r="70" ht="75" spans="1:5">
-      <c r="A70" s="76" t="s">
+      <c r="A70" s="67" t="s">
         <v>60</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="75" t="s">
+      <c r="C70" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="D70" s="87" t="s">
+      <c r="D70" s="78" t="s">
         <v>102</v>
       </c>
       <c r="E70" s="3"/>
     </row>
     <row r="71" ht="45" spans="1:5">
-      <c r="A71" s="76" t="s">
+      <c r="A71" s="67" t="s">
         <v>63</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -4717,273 +4690,271 @@
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="42" style="38" customWidth="1"/>
-    <col min="2" max="2" width="42.8571428571429" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.2380952380952" style="3" customWidth="1"/>
+    <col min="2" max="2" width="46.3619047619048" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.952380952381" style="3" customWidth="1"/>
     <col min="4" max="4" width="13.3714285714286" style="3" customWidth="1"/>
     <col min="5" max="5" width="22.7238095238095" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:5">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:5">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="47">
-        <v>3115502.69</v>
-      </c>
-      <c r="D4" s="47">
+      <c r="C4" s="43">
+        <v>5710027</v>
+      </c>
+      <c r="D4" s="43">
         <v>3015502.69</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="24">
         <v>2715502.69</v>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1" spans="1:5">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="47">
-        <v>1</v>
-      </c>
-      <c r="D5" s="47">
+      <c r="C5" s="43">
+        <v>4</v>
+      </c>
+      <c r="D5" s="43">
         <f>C5</f>
-        <v>1</v>
-      </c>
-      <c r="E5" s="48">
+        <v>4</v>
+      </c>
+      <c r="E5" s="24">
         <f>D5</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:5">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="47">
-        <v>115000</v>
-      </c>
-      <c r="D6" s="47">
-        <v>215000</v>
-      </c>
-      <c r="E6" s="47">
+      <c r="C6" s="43">
+        <v>66000</v>
+      </c>
+      <c r="D6" s="43">
+        <v>251001</v>
+      </c>
+      <c r="E6" s="43">
         <v>200000</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:5">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="47">
-        <v>14200</v>
-      </c>
-      <c r="D7" s="47">
-        <v>27000</v>
-      </c>
-      <c r="E7" s="47">
+      <c r="C7" s="43">
+        <v>2200</v>
+      </c>
+      <c r="D7" s="43">
+        <v>47010</v>
+      </c>
+      <c r="E7" s="43">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="43">
         <f>C6-C7</f>
-        <v>100800</v>
-      </c>
-      <c r="D8" s="47">
+        <v>63800</v>
+      </c>
+      <c r="D8" s="43">
         <f>D6-D7</f>
-        <v>188000</v>
-      </c>
-      <c r="E8" s="47">
+        <v>203991</v>
+      </c>
+      <c r="E8" s="43">
         <f>E6-E7</f>
         <v>200000</v>
       </c>
     </row>
     <row r="9" ht="71" customHeight="1" spans="1:5">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="43">
         <f>3%*C8</f>
-        <v>3024</v>
-      </c>
-      <c r="D9" s="47">
+        <v>1914</v>
+      </c>
+      <c r="D9" s="43">
         <f>3%*D8</f>
-        <v>5640</v>
-      </c>
-      <c r="E9" s="47">
+        <v>6119.73</v>
+      </c>
+      <c r="E9" s="43">
         <f>3%*E8</f>
         <v>6000</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:5">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="43">
         <f>C8-C9</f>
-        <v>97776</v>
-      </c>
-      <c r="D10" s="47">
+        <v>61886</v>
+      </c>
+      <c r="D10" s="43">
         <f>D8-D9</f>
-        <v>182360</v>
-      </c>
-      <c r="E10" s="47">
+        <v>197871.27</v>
+      </c>
+      <c r="E10" s="43">
         <f>E8-E9</f>
         <v>194000</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:5">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="64">
+      <c r="C11" s="56">
         <f>15%*C4</f>
-        <v>467325.4035</v>
-      </c>
-      <c r="D11" s="64">
+        <v>856504.05</v>
+      </c>
+      <c r="D11" s="56">
         <f>15%*D4</f>
         <v>452325.4035</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="56">
         <f>15%*E4</f>
         <v>407325.4035</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:5">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="43">
         <f>75%*C10</f>
-        <v>73332</v>
-      </c>
-      <c r="D12" s="47">
+        <v>46414.5</v>
+      </c>
+      <c r="D12" s="43">
         <f>75%*D10</f>
-        <v>136770</v>
-      </c>
-      <c r="E12" s="47">
+        <v>148403.4525</v>
+      </c>
+      <c r="E12" s="43">
         <f>75%*E10</f>
         <v>145500</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="47">
+      <c r="C13" s="43">
         <f>C12</f>
-        <v>73332</v>
-      </c>
-      <c r="D13" s="47">
+        <v>46414.5</v>
+      </c>
+      <c r="D13" s="43">
         <f>D12</f>
-        <v>136770</v>
-      </c>
-      <c r="E13" s="47">
+        <v>148403.4525</v>
+      </c>
+      <c r="E13" s="43">
         <f>E12</f>
         <v>145500</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:5">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47">
+      <c r="C14" s="43"/>
+      <c r="D14" s="43">
         <f>C15</f>
-        <v>73332</v>
-      </c>
-      <c r="E14" s="47">
+        <v>46414.5</v>
+      </c>
+      <c r="E14" s="43">
         <f>D15+C15</f>
-        <v>136770</v>
+        <v>148403.4525</v>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1" spans="1:5">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="65">
+      <c r="C15" s="57">
         <f>C13-C14</f>
-        <v>73332</v>
-      </c>
-      <c r="D15" s="65">
+        <v>46414.5</v>
+      </c>
+      <c r="D15" s="57">
         <f>D13-D14</f>
-        <v>63438</v>
-      </c>
-      <c r="E15" s="65">
+        <v>101988.9525</v>
+      </c>
+      <c r="E15" s="57">
         <f>E13-E14</f>
-        <v>8730</v>
+        <v>-2903.45249999998</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5004,115 +4975,115 @@
   <cols>
     <col min="1" max="1" width="42" style="38" customWidth="1"/>
     <col min="2" max="2" width="40" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.4952380952381" style="39" customWidth="1"/>
-    <col min="4" max="4" width="23.3714285714286" style="40" customWidth="1"/>
+    <col min="3" max="3" width="16.4952380952381" style="24" customWidth="1"/>
+    <col min="4" max="4" width="23.3714285714286" style="27" customWidth="1"/>
     <col min="5" max="5" width="24.8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:15">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:15">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="42"/>
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:15">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="43">
         <v>5500001</v>
       </c>
-      <c r="D4" s="48">
+      <c r="D4" s="24">
         <v>3000000</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="24">
         <v>9200001</v>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1" spans="1:15">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="43">
         <v>1</v>
       </c>
-      <c r="D5" s="48">
+      <c r="D5" s="24">
         <f>C5</f>
         <v>1</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="24">
         <f>D5</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:15">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="43">
         <v>1100500</v>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="24">
         <v>1100000</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="24">
         <v>1800000</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:15">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="43">
         <v>3800</v>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="24">
         <v>1200</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="24">
         <v>20800</v>
       </c>
-      <c r="L7" s="50">
+      <c r="L7" s="45">
         <v>15000</v>
       </c>
       <c r="N7">
@@ -5120,21 +5091,21 @@
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:15">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="43">
         <f>C6-C7</f>
         <v>1096700</v>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="24">
         <f>D6-D7</f>
         <v>1098800</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="24">
         <f>E6-E7</f>
         <v>1779200</v>
       </c>
@@ -5149,64 +5120,62 @@
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:15">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="51">
+      <c r="C9" s="46">
         <f>75%*C8</f>
         <v>822525</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="46">
         <f>75%*D8</f>
         <v>824100</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="46">
         <f>75%*E8</f>
         <v>1334400</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:15">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="43">
         <v>0</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="24">
         <f>C11</f>
         <v>822525</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="24">
         <f>D11+C11</f>
         <v>824100</v>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1" spans="1:15">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="47">
+      <c r="C11" s="43">
         <f>C9-C10</f>
         <v>822525</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="47">
         <f>D9-D10</f>
         <v>1575</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="5">
         <f>E9-E10</f>
         <v>510300</v>
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="59"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="61"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5227,116 +5196,116 @@
   <cols>
     <col min="1" max="1" width="42" style="38" customWidth="1"/>
     <col min="2" max="2" width="40" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.4952380952381" style="39" customWidth="1"/>
-    <col min="4" max="4" width="23.3714285714286" style="40" customWidth="1"/>
+    <col min="3" max="3" width="16.4952380952381" style="24" customWidth="1"/>
+    <col min="4" max="4" width="23.3714285714286" style="27" customWidth="1"/>
     <col min="5" max="5" width="24.8" customWidth="1"/>
     <col min="9" max="9" width="20.647619047619" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="5" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:15">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:15">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="42"/>
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:15">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="43">
         <v>5500001</v>
       </c>
-      <c r="D4" s="48">
+      <c r="D4" s="24">
         <v>3000000</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="24">
         <v>9200001</v>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1" spans="1:15">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="43">
         <v>1</v>
       </c>
-      <c r="D5" s="48">
+      <c r="D5" s="24">
         <f>C5</f>
         <v>1</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="24">
         <f>D5</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:15">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="43">
         <v>1100500</v>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="24">
         <v>1100000</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="24">
         <v>1800000</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:15">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="43">
         <v>3800</v>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="24">
         <v>1200</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="24">
         <v>20800</v>
       </c>
-      <c r="L7" s="50">
+      <c r="L7" s="45">
         <v>15000</v>
       </c>
       <c r="N7">
@@ -5344,21 +5313,21 @@
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:15">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="43">
         <f>C6-C7</f>
         <v>1096700</v>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="24">
         <f>D6-D7</f>
         <v>1098800</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="24">
         <f>E6-E7</f>
         <v>1779200</v>
       </c>
@@ -5373,133 +5342,131 @@
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:15">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="51">
+      <c r="C9" s="46">
         <f>75%*C8</f>
         <v>822525</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="46">
         <f>75%*D8</f>
         <v>824100</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="46">
         <f>75%*E8</f>
         <v>1334400</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:15">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="43">
         <v>0</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="24">
         <f>C11</f>
         <v>822525</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="24">
         <f>D11+C11</f>
         <v>824100</v>
       </c>
     </row>
     <row r="11" ht="125" customHeight="1" spans="1:15">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="47">
+      <c r="C11" s="43">
         <f>C9-C10</f>
         <v>822525</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="47">
         <f>D9-D10</f>
         <v>1575</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="5">
         <f>E9-E10</f>
         <v>510300</v>
       </c>
-      <c r="I11" s="53" t="s">
+      <c r="I11" s="48" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="56">
+      <c r="B12" s="50"/>
+      <c r="C12" s="51">
         <v>3000000</v>
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="52" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="29"/>
-      <c r="C13" s="58">
+      <c r="C13" s="5">
         <v>2680800</v>
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="52" t="s">
         <v>136</v>
       </c>
       <c r="B14" s="29"/>
-      <c r="C14" s="58">
+      <c r="C14" s="5">
         <f>C13</f>
         <v>2680800</v>
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="57" t="s">
+      <c r="A15" s="52" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="29"/>
-      <c r="C15" s="58">
+      <c r="C15" s="5">
         <f>75%*C14</f>
         <v>2010600</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="52" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="29"/>
-      <c r="C16" s="58">
+      <c r="C16" s="5">
         <f>15%*C12</f>
         <v>450000</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="57"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="29"/>
-      <c r="C17" s="58" t="b">
+      <c r="C17" s="5" t="b">
         <f>IF(C15&gt;C16,C16=C15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="52" t="s">
         <v>137</v>
       </c>
       <c r="B18" s="29"/>
-      <c r="C18" s="58">
+      <c r="C18" s="5">
         <f>15%*C14</f>
         <v>402120</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="57"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="29"/>
-      <c r="C19" s="58"/>
+      <c r="C19" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/MU/BRD - test Doc/MU user manual infoneo (2).xlsx
+++ b/MU/BRD - test Doc/MU user manual infoneo (2).xlsx
@@ -4744,7 +4744,7 @@
         <v>3015502.69</v>
       </c>
       <c r="E4" s="24">
-        <v>2715502.69</v>
+        <v>5710027</v>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1" spans="1:5">
@@ -4780,7 +4780,7 @@
         <v>251001</v>
       </c>
       <c r="E6" s="43">
-        <v>200000</v>
+        <v>574001</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:5">
@@ -4797,7 +4797,7 @@
         <v>47010</v>
       </c>
       <c r="E7" s="43">
-        <v>0</v>
+        <v>277110</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="E8" s="43">
         <f>E6-E7</f>
-        <v>200000</v>
+        <v>296891</v>
       </c>
     </row>
     <row r="9" ht="71" customHeight="1" spans="1:5">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="E9" s="43">
         <f>3%*E8</f>
-        <v>6000</v>
+        <v>8906.73</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:5">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="E10" s="43">
         <f>E8-E9</f>
-        <v>194000</v>
+        <v>287984.27</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:5">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="E11" s="56">
         <f>15%*E4</f>
-        <v>407325.4035</v>
+        <v>856504.05</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:5">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E12" s="43">
         <f>75%*E10</f>
-        <v>145500</v>
+        <v>215988.2025</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="E13" s="43">
         <f>E12</f>
-        <v>145500</v>
+        <v>215988.2025</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:5">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="E15" s="57">
         <f>E13-E14</f>
-        <v>-2903.45249999998</v>
+        <v>67584.75</v>
       </c>
     </row>
     <row r="16" spans="1:5">

--- a/MU/BRD - test Doc/MU user manual infoneo (2).xlsx
+++ b/MU/BRD - test Doc/MU user manual infoneo (2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="24000" windowHeight="9600" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Flow" sheetId="1" r:id="rId1"/>
@@ -5660,33 +5660,33 @@
         <v>10000</v>
       </c>
       <c r="C15" s="34">
-        <v>46082</v>
+        <v>47209</v>
       </c>
       <c r="D15" s="34">
-        <v>46477</v>
+        <v>47573</v>
       </c>
       <c r="E15" s="35">
         <f>DATEDIF(C15,D15,"d")+1</f>
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="F15" s="37">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="G15" s="35">
         <f>IF(K15="Closed",0,B15*F15*(E15/365))</f>
-        <v>108.493150684932</v>
+        <v>50</v>
       </c>
       <c r="H15" s="35">
         <f>G15*9%</f>
-        <v>9.76438356164384</v>
+        <v>4.5</v>
       </c>
       <c r="I15" s="35">
         <f>18%*G15</f>
-        <v>19.5287671232877</v>
+        <v>9</v>
       </c>
       <c r="J15" s="35">
         <f>G15+H15+I15</f>
-        <v>137.786301369863</v>
+        <v>63.5</v>
       </c>
       <c r="K15" s="35" t="s">
         <v>160</v>

--- a/MU/BRD - test Doc/MU user manual infoneo (2).xlsx
+++ b/MU/BRD - test Doc/MU user manual infoneo (2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" firstSheet="1" activeTab="4"/>
+    <workbookView windowWidth="24000" windowHeight="9600" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Flow" sheetId="1" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
     <sheet name="Sheet4" sheetId="9" r:id="rId8"/>
     <sheet name="Sheet3" sheetId="10" r:id="rId9"/>
+    <sheet name="Sheet5" sheetId="13" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet2!$A$1:$H$32</definedName>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="317">
   <si>
     <t>Category</t>
   </si>
@@ -1991,6 +1992,48 @@
   </si>
   <si>
     <t>22L</t>
+  </si>
+  <si>
+    <t>Sr.No</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Existing Feature</t>
+  </si>
+  <si>
+    <t>Proposed feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New CG </t>
+  </si>
+  <si>
+    <t>Field name - Loan Disbursed Amount</t>
+  </si>
+  <si>
+    <t>The field/column name should be changed from “Loan Disbursed Amount” to “Total Loan Disbursed Amount (Inputted by MLI) on Excel upload new cg file (Impact on Search &amp; View field also)</t>
+  </si>
+  <si>
+    <t>CG fee Calculation (Base Period-New CG)</t>
+  </si>
+  <si>
+    <t>Mudra portfolio: 1% CG fee calculated based on the sanction amount for both TL and WC accounts</t>
+  </si>
+  <si>
+    <t>For Mudra Portfolios: 0.75% CG fee calculated based on the disbursed amount for TL account and sanctioned amount for WC accounts</t>
+  </si>
+  <si>
+    <t>For SHG Portfolios: No change, existing provision will be continued.</t>
+  </si>
+  <si>
+    <t>same - 0.25% on outstanding amount for both TL and WC accounts.</t>
+  </si>
+  <si>
+    <t>CG fee cacluation to be changes in Tentative bill &amp; Final Bill as well.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This will impact on Update CG ( Need to check for disbusred amount for TL) &amp; Claim (Crystilised amount - check on disbusred amount) Need to confirm with Business team </t>
   </si>
 </sst>
 </file>
@@ -4683,6 +4726,84 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="35.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="40.8571428571429" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -4738,13 +4859,13 @@
         <v>111</v>
       </c>
       <c r="C4" s="43">
-        <v>5710027</v>
+        <v>16500000</v>
       </c>
       <c r="D4" s="43">
-        <v>3015502.69</v>
+        <v>16000000</v>
       </c>
       <c r="E4" s="24">
-        <v>5710027</v>
+        <v>16000000</v>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1" spans="1:5">
@@ -4774,13 +4895,13 @@
         <v>115</v>
       </c>
       <c r="C6" s="43">
-        <v>66000</v>
+        <v>200000</v>
       </c>
       <c r="D6" s="43">
-        <v>251001</v>
+        <v>400000</v>
       </c>
       <c r="E6" s="43">
-        <v>574001</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:5">
@@ -4791,13 +4912,13 @@
         <v>117</v>
       </c>
       <c r="C7" s="43">
-        <v>2200</v>
+        <v>26800</v>
       </c>
       <c r="D7" s="43">
-        <v>47010</v>
+        <v>52400</v>
       </c>
       <c r="E7" s="43">
-        <v>277110</v>
+        <v>65200</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5">
@@ -4809,15 +4930,15 @@
       </c>
       <c r="C8" s="43">
         <f>C6-C7</f>
-        <v>63800</v>
+        <v>173200</v>
       </c>
       <c r="D8" s="43">
         <f>D6-D7</f>
-        <v>203991</v>
+        <v>347600</v>
       </c>
       <c r="E8" s="43">
         <f>E6-E7</f>
-        <v>296891</v>
+        <v>434800</v>
       </c>
     </row>
     <row r="9" ht="71" customHeight="1" spans="1:5">
@@ -4829,15 +4950,15 @@
       </c>
       <c r="C9" s="43">
         <f>3%*C8</f>
-        <v>1914</v>
+        <v>5196</v>
       </c>
       <c r="D9" s="43">
         <f>3%*D8</f>
-        <v>6119.73</v>
+        <v>10428</v>
       </c>
       <c r="E9" s="43">
         <f>3%*E8</f>
-        <v>8906.73</v>
+        <v>13044</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:5">
@@ -4849,15 +4970,15 @@
       </c>
       <c r="C10" s="43">
         <f>C8-C9</f>
-        <v>61886</v>
+        <v>168004</v>
       </c>
       <c r="D10" s="43">
         <f>D8-D9</f>
-        <v>197871.27</v>
+        <v>337172</v>
       </c>
       <c r="E10" s="43">
         <f>E8-E9</f>
-        <v>287984.27</v>
+        <v>421756</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:5">
@@ -4869,15 +4990,15 @@
       </c>
       <c r="C11" s="56">
         <f>15%*C4</f>
-        <v>856504.05</v>
+        <v>2475000</v>
       </c>
       <c r="D11" s="56">
         <f>15%*D4</f>
-        <v>452325.4035</v>
+        <v>2400000</v>
       </c>
       <c r="E11" s="56">
         <f>15%*E4</f>
-        <v>856504.05</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:5">
@@ -4889,15 +5010,15 @@
       </c>
       <c r="C12" s="43">
         <f>75%*C10</f>
-        <v>46414.5</v>
+        <v>126003</v>
       </c>
       <c r="D12" s="43">
         <f>75%*D10</f>
-        <v>148403.4525</v>
+        <v>252879</v>
       </c>
       <c r="E12" s="43">
         <f>75%*E10</f>
-        <v>215988.2025</v>
+        <v>316317</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
@@ -4906,15 +5027,15 @@
       </c>
       <c r="C13" s="43">
         <f>C12</f>
-        <v>46414.5</v>
+        <v>126003</v>
       </c>
       <c r="D13" s="43">
         <f>D12</f>
-        <v>148403.4525</v>
+        <v>252879</v>
       </c>
       <c r="E13" s="43">
         <f>E12</f>
-        <v>215988.2025</v>
+        <v>316317</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:5">
@@ -4927,11 +5048,11 @@
       <c r="C14" s="43"/>
       <c r="D14" s="43">
         <f>C15</f>
-        <v>46414.5</v>
+        <v>126003</v>
       </c>
       <c r="E14" s="43">
         <f>D15+C15</f>
-        <v>148403.4525</v>
+        <v>252879</v>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1" spans="1:5">
@@ -4940,15 +5061,15 @@
       </c>
       <c r="C15" s="57">
         <f>C13-C14</f>
-        <v>46414.5</v>
+        <v>126003</v>
       </c>
       <c r="D15" s="57">
         <f>D13-D14</f>
-        <v>101988.9525</v>
+        <v>126876</v>
       </c>
       <c r="E15" s="57">
         <f>E13-E14</f>
-        <v>67584.75</v>
+        <v>63438</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5534,29 +5655,29 @@
     </row>
     <row r="3" s="32" customFormat="1" spans="1:14">
       <c r="A3" s="34">
-        <v>46174</v>
+        <v>48670</v>
       </c>
       <c r="B3" s="34">
-        <v>46477</v>
+        <v>49034</v>
       </c>
       <c r="C3" s="35">
         <f>B3-A3+1</f>
-        <v>304</v>
+        <v>365</v>
       </c>
       <c r="D3" s="36">
         <f>1%*E3*C3/365</f>
-        <v>832.876712328767</v>
+        <v>1000</v>
       </c>
       <c r="E3" s="35">
         <v>100000</v>
       </c>
       <c r="F3" s="35">
         <f>D3*18%</f>
-        <v>149.917808219178</v>
+        <v>180</v>
       </c>
       <c r="G3" s="35">
         <f>D3+F3</f>
-        <v>982.794520547945</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="4" s="32" customFormat="1"/>

--- a/MU/BRD - test Doc/MU user manual infoneo (2).xlsx
+++ b/MU/BRD - test Doc/MU user manual infoneo (2).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" firstSheet="3" activeTab="4"/>
+    <workbookView windowWidth="24000" windowHeight="9600" firstSheet="3" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Flow" sheetId="1" r:id="rId1"/>
@@ -15,8 +15,7 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId6"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId7"/>
     <sheet name="Sheet4" sheetId="9" r:id="rId8"/>
-    <sheet name="Sheet3" sheetId="10" r:id="rId9"/>
-    <sheet name="Sheet5" sheetId="13" r:id="rId10"/>
+    <sheet name="Sheet3" sheetId="14" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Sheet2!$A$1:$H$32</definedName>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="306">
   <si>
     <t>Category</t>
   </si>
@@ -1970,70 +1969,37 @@
     <t>1st Update CG , then claim , settle , next CP upload CG for same loan ac</t>
   </si>
   <si>
-    <t>Sanct</t>
-  </si>
-  <si>
-    <t>10 Record</t>
-  </si>
-  <si>
-    <t>5L</t>
-  </si>
-  <si>
-    <t>6L</t>
-  </si>
-  <si>
-    <t>cryz</t>
-  </si>
-  <si>
-    <t>21L</t>
-  </si>
-  <si>
-    <t>Max payout on claim</t>
-  </si>
-  <si>
-    <t>22L</t>
-  </si>
-  <si>
-    <t>Sr.No</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>Existing Feature</t>
-  </si>
-  <si>
-    <t>Proposed feature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New CG </t>
-  </si>
-  <si>
-    <t>Field name - Loan Disbursed Amount</t>
-  </si>
-  <si>
-    <t>The field/column name should be changed from “Loan Disbursed Amount” to “Total Loan Disbursed Amount (Inputted by MLI) on Excel upload new cg file (Impact on Search &amp; View field also)</t>
-  </si>
-  <si>
-    <t>CG fee Calculation (Base Period-New CG)</t>
-  </si>
-  <si>
-    <t>Mudra portfolio: 1% CG fee calculated based on the sanction amount for both TL and WC accounts</t>
-  </si>
-  <si>
-    <t>For Mudra Portfolios: 0.75% CG fee calculated based on the disbursed amount for TL account and sanctioned amount for WC accounts</t>
-  </si>
-  <si>
-    <t>For SHG Portfolios: No change, existing provision will be continued.</t>
-  </si>
-  <si>
-    <t>same - 0.25% on outstanding amount for both TL and WC accounts.</t>
-  </si>
-  <si>
-    <t>CG fee cacluation to be changes in Tentative bill &amp; Final Bill as well.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This will impact on Update CG ( Need to check for disbusred amount for TL) &amp; Claim (Crystilised amount - check on disbusred amount) Need to confirm with Business team </t>
+    <t>Retro</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>SHG</t>
+  </si>
+  <si>
+    <t>FY 26-27</t>
+  </si>
+  <si>
+    <t>Upload time span</t>
+  </si>
+  <si>
+    <t>apr - jun 26</t>
+  </si>
+  <si>
+    <t>july - sept</t>
+  </si>
+  <si>
+    <t>oct - dec</t>
+  </si>
+  <si>
+    <t>Jan - march</t>
+  </si>
+  <si>
+    <t>apr - jun 27</t>
+  </si>
+  <si>
+    <t>july to 31 march 28</t>
   </si>
 </sst>
 </file>
@@ -2979,14 +2945,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -3757,947 +3729,947 @@
   <dimension ref="A1:Z71"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7142857142857" style="61" customWidth="1"/>
+    <col min="1" max="1" width="22.7142857142857" style="63" customWidth="1"/>
     <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="49.8571428571429" style="48" customWidth="1"/>
+    <col min="3" max="3" width="49.8571428571429" style="50" customWidth="1"/>
     <col min="4" max="4" width="46.8571428571429" customWidth="1"/>
     <col min="5" max="5" width="57.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:26">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="E1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
-      <c r="U1" s="64"/>
-      <c r="V1" s="64"/>
-      <c r="W1" s="64"/>
-      <c r="X1" s="64"/>
-      <c r="Y1" s="64"/>
-      <c r="Z1" s="64"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="66"/>
+      <c r="Y1" s="66"/>
+      <c r="Z1" s="66"/>
     </row>
     <row r="2" ht="135" spans="1:26">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="75" spans="1:26">
-      <c r="A3" s="67"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="69"/>
+      <c r="B3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" ht="75" spans="1:26">
-      <c r="A4" s="67"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="69"/>
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="3"/>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="68"/>
-      <c r="B5" s="69"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
+      <c r="A5" s="70"/>
+      <c r="B5" s="71"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
     </row>
     <row r="6" ht="75" spans="1:26">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="71" t="s">
+      <c r="D6" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:26">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="66" t="s">
+      <c r="D7" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="3"/>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" ht="56" customHeight="1" spans="1:26">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="66" t="s">
+      <c r="C8" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" ht="60" spans="1:26">
-      <c r="A9" s="67"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="69"/>
+      <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" ht="60" spans="1:26">
-      <c r="A10" s="67" t="s">
+      <c r="A10" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="3"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" customFormat="1" ht="60" spans="1:26">
-      <c r="A11" s="67" t="s">
+      <c r="A11" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="3"/>
+      <c r="E11" s="5"/>
     </row>
     <row r="12" customFormat="1" ht="45" spans="1:26">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
     </row>
     <row r="13" customFormat="1" ht="60" spans="1:26">
-      <c r="A13" s="67"/>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="69"/>
+      <c r="B13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" customFormat="1" ht="60" spans="1:26">
-      <c r="A14" s="67" t="s">
+      <c r="A14" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="3"/>
+      <c r="E14" s="5"/>
     </row>
     <row r="15" ht="60" spans="1:26">
-      <c r="A15" s="67" t="s">
+      <c r="A15" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="66" t="s">
+      <c r="D15" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="3"/>
+      <c r="E15" s="5"/>
     </row>
     <row r="16" ht="45" spans="1:26">
-      <c r="A16" s="67" t="s">
+      <c r="A16" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C16" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" ht="60" spans="1:5">
-      <c r="A17" s="67"/>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="69"/>
+      <c r="B17" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="66" t="s">
+      <c r="C17" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
     </row>
     <row r="18" customFormat="1" ht="60" spans="1:5">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
     </row>
     <row r="19" ht="60" spans="1:5">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="66" t="s">
+      <c r="D19" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="3"/>
+      <c r="E19" s="5"/>
     </row>
     <row r="20" ht="45" spans="1:5">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
     </row>
     <row r="21" ht="60" spans="1:5">
-      <c r="A21" s="67"/>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="69"/>
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
     </row>
     <row r="22" ht="90" spans="1:5">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="66" t="s">
+      <c r="C22" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
     </row>
     <row r="23" ht="65" customHeight="1" spans="1:5">
-      <c r="A23" s="67" t="s">
+      <c r="A23" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="71" t="s">
+      <c r="D23" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="24" ht="65" customHeight="1" spans="1:5">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="71" t="s">
+      <c r="D24" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" s="58" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A25" s="72" t="s">
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25" s="60" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A25" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="73"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="74"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="76"/>
     </row>
     <row r="26" ht="90" spans="1:5">
-      <c r="A26" s="75" t="s">
+      <c r="A26" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="76" t="s">
+      <c r="D26" s="78" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="54"/>
+      <c r="E26" s="56"/>
     </row>
     <row r="27" ht="45" spans="1:5">
-      <c r="A27" s="75"/>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="77"/>
+      <c r="B27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="66" t="s">
+      <c r="C27" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
     </row>
     <row r="28" ht="60" spans="1:5">
-      <c r="A28" s="77"/>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="79"/>
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
     </row>
     <row r="29" ht="75" spans="1:5">
-      <c r="A29" s="67" t="s">
+      <c r="A29" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="78" t="s">
+      <c r="D29" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="3"/>
+      <c r="E29" s="5"/>
     </row>
     <row r="30" ht="45" spans="1:5">
-      <c r="A30" s="67" t="s">
+      <c r="A30" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
     </row>
     <row r="31" ht="55" customHeight="1" spans="1:5">
-      <c r="A31" s="67" t="s">
+      <c r="A31" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
     </row>
     <row r="32" ht="45" spans="1:5">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D32" s="66"/>
-      <c r="E32" s="3"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="5"/>
     </row>
     <row r="33" ht="45" spans="1:5">
-      <c r="A33" s="23"/>
-      <c r="B33" s="3" t="s">
+      <c r="A33" s="25"/>
+      <c r="B33" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="66"/>
-      <c r="E33" s="3"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="5"/>
     </row>
     <row r="34" ht="45" spans="1:5">
-      <c r="A34" s="23"/>
-      <c r="B34" s="3" t="s">
+      <c r="A34" s="25"/>
+      <c r="B34" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="66" t="s">
+      <c r="C34" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="66"/>
-      <c r="E34" s="3"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="5"/>
     </row>
     <row r="35" ht="75" spans="1:5">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="66" t="s">
+      <c r="C35" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="66" t="s">
+      <c r="D35" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="3"/>
+      <c r="E35" s="5"/>
     </row>
     <row r="36" ht="75" spans="1:5">
-      <c r="A36" s="23"/>
-      <c r="B36" s="3" t="s">
+      <c r="A36" s="25"/>
+      <c r="B36" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="66" t="s">
+      <c r="C36" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
     </row>
     <row r="37" ht="45" spans="1:5">
-      <c r="A37" s="23"/>
-      <c r="B37" s="3" t="s">
+      <c r="A37" s="25"/>
+      <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="66" t="s">
+      <c r="C37" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
     </row>
     <row r="38" ht="60" spans="1:5">
-      <c r="A38" s="79" t="s">
+      <c r="A38" s="81" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="66" t="s">
+      <c r="C38" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="66"/>
-      <c r="E38" s="3" t="s">
+      <c r="D38" s="68"/>
+      <c r="E38" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" ht="60" spans="1:5">
-      <c r="A39" s="75"/>
-      <c r="B39" s="3" t="s">
+      <c r="A39" s="77"/>
+      <c r="B39" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="66" t="s">
+      <c r="C39" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="66"/>
-      <c r="E39" s="3"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="5"/>
     </row>
     <row r="40" ht="90" spans="1:5">
-      <c r="A40" s="79" t="s">
+      <c r="A40" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="66" t="s">
+      <c r="C40" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="66" t="s">
+      <c r="D40" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="3"/>
+      <c r="E40" s="5"/>
     </row>
     <row r="41" ht="75" spans="1:5">
-      <c r="A41" s="75"/>
-      <c r="B41" s="3" t="s">
+      <c r="A41" s="77"/>
+      <c r="B41" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="66" t="s">
+      <c r="C41" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
     </row>
     <row r="42" ht="45" spans="1:5">
-      <c r="A42" s="77"/>
-      <c r="B42" s="3" t="s">
+      <c r="A42" s="79"/>
+      <c r="B42" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="66" t="s">
+      <c r="C42" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
     </row>
     <row r="43" ht="75" spans="1:5">
-      <c r="A43" s="67" t="s">
+      <c r="A43" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D43" s="78" t="s">
+      <c r="D43" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="3"/>
-    </row>
-    <row r="44" s="59" customFormat="1" ht="45" spans="1:5">
-      <c r="A44" s="65" t="s">
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44" s="61" customFormat="1" ht="45" spans="1:5">
+      <c r="A44" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="22" t="s">
+      <c r="B44" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="80" t="s">
+      <c r="C44" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="D44" s="22" t="s">
+      <c r="D44" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="E44" s="22"/>
+      <c r="E44" s="24"/>
     </row>
     <row r="45" ht="75" spans="1:5">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D45" s="66" t="s">
+      <c r="D45" s="68" t="s">
         <v>90</v>
       </c>
-      <c r="E45" s="3"/>
+      <c r="E45" s="5"/>
     </row>
     <row r="46" ht="75" spans="1:5">
-      <c r="A46" s="23"/>
-      <c r="B46" s="3" t="s">
+      <c r="A46" s="25"/>
+      <c r="B46" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="66" t="s">
+      <c r="C46" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
     </row>
     <row r="47" ht="45" spans="1:5">
-      <c r="A47" s="23"/>
-      <c r="B47" s="3" t="s">
+      <c r="A47" s="25"/>
+      <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="66" t="s">
+      <c r="C47" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
     </row>
     <row r="48" ht="60" spans="1:5">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="66" t="s">
+      <c r="C48" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="D48" s="66"/>
-      <c r="E48" s="3" t="s">
+      <c r="D48" s="68"/>
+      <c r="E48" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="49" ht="60" spans="1:5">
-      <c r="A49" s="23"/>
-      <c r="B49" s="3" t="s">
+      <c r="A49" s="25"/>
+      <c r="B49" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="66" t="s">
+      <c r="C49" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="D49" s="66"/>
-      <c r="E49" s="3"/>
+      <c r="D49" s="68"/>
+      <c r="E49" s="5"/>
     </row>
     <row r="50" ht="90" spans="1:5">
-      <c r="A50" s="79" t="s">
+      <c r="A50" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="66" t="s">
+      <c r="C50" s="68" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="66" t="s">
+      <c r="D50" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="E50" s="3"/>
+      <c r="E50" s="5"/>
     </row>
     <row r="51" ht="75" spans="1:5">
-      <c r="A51" s="75"/>
-      <c r="B51" s="3" t="s">
+      <c r="A51" s="77"/>
+      <c r="B51" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="66" t="s">
+      <c r="C51" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
     </row>
     <row r="52" ht="45" spans="1:5">
-      <c r="A52" s="77"/>
-      <c r="B52" s="3" t="s">
+      <c r="A52" s="79"/>
+      <c r="B52" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="66" t="s">
+      <c r="C52" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
     </row>
     <row r="53" ht="75" spans="1:5">
-      <c r="A53" s="67" t="s">
+      <c r="A53" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C53" s="66" t="s">
+      <c r="C53" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="78" t="s">
+      <c r="D53" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="E53" s="3"/>
-    </row>
-    <row r="54" s="59" customFormat="1" ht="45" spans="1:5">
-      <c r="A54" s="65" t="s">
+      <c r="E53" s="5"/>
+    </row>
+    <row r="54" s="61" customFormat="1" ht="45" spans="1:5">
+      <c r="A54" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="22" t="s">
+      <c r="B54" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C54" s="80" t="s">
+      <c r="C54" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="D54" s="22" t="s">
+      <c r="D54" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="E54" s="22"/>
+      <c r="E54" s="24"/>
     </row>
     <row r="56" ht="75" spans="1:5">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="66" t="s">
+      <c r="C56" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="66" t="s">
+      <c r="D56" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="E56" s="3"/>
+      <c r="E56" s="5"/>
     </row>
     <row r="57" ht="75" spans="1:5">
-      <c r="A57" s="23"/>
-      <c r="B57" s="3" t="s">
+      <c r="A57" s="25"/>
+      <c r="B57" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="66" t="s">
+      <c r="C57" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
     </row>
     <row r="58" ht="45" spans="1:5">
-      <c r="A58" s="23"/>
-      <c r="B58" s="3" t="s">
+      <c r="A58" s="25"/>
+      <c r="B58" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="66" t="s">
+      <c r="C58" s="68" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
     </row>
     <row r="59" ht="60" spans="1:5">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="66" t="s">
+      <c r="C59" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="D59" s="66"/>
-      <c r="E59" s="3" t="s">
+      <c r="D59" s="68"/>
+      <c r="E59" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="60" ht="60" spans="1:5">
-      <c r="A60" s="23"/>
-      <c r="B60" s="3" t="s">
+      <c r="A60" s="25"/>
+      <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="66" t="s">
+      <c r="C60" s="68" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="66"/>
-      <c r="E60" s="3"/>
-    </row>
-    <row r="61" s="60" customFormat="1" ht="90" spans="1:5">
-      <c r="A61" s="81" t="s">
+      <c r="D60" s="68"/>
+      <c r="E60" s="5"/>
+    </row>
+    <row r="61" s="62" customFormat="1" ht="90" spans="1:5">
+      <c r="A61" s="83" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="82" t="s">
+      <c r="B61" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="83" t="s">
+      <c r="C61" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="83" t="s">
+      <c r="D61" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="E61" s="82"/>
-    </row>
-    <row r="62" s="60" customFormat="1" ht="75" spans="1:5">
-      <c r="A62" s="84"/>
-      <c r="B62" s="82" t="s">
+      <c r="E61" s="84"/>
+    </row>
+    <row r="62" s="62" customFormat="1" ht="75" spans="1:5">
+      <c r="A62" s="86"/>
+      <c r="B62" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="C62" s="83" t="s">
+      <c r="C62" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="D62" s="82"/>
-      <c r="E62" s="82"/>
-    </row>
-    <row r="63" s="60" customFormat="1" ht="45" spans="1:5">
-      <c r="A63" s="85"/>
-      <c r="B63" s="82" t="s">
+      <c r="D62" s="84"/>
+      <c r="E62" s="84"/>
+    </row>
+    <row r="63" s="62" customFormat="1" ht="45" spans="1:5">
+      <c r="A63" s="87"/>
+      <c r="B63" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="83" t="s">
+      <c r="C63" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="D63" s="82"/>
-      <c r="E63" s="82"/>
+      <c r="D63" s="84"/>
+      <c r="E63" s="84"/>
     </row>
     <row r="64" ht="75" spans="1:5">
-      <c r="A64" s="67" t="s">
+      <c r="A64" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C64" s="66" t="s">
+      <c r="C64" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D64" s="78" t="s">
+      <c r="D64" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="E64" s="3"/>
-    </row>
-    <row r="65" s="59" customFormat="1" ht="45" spans="1:5">
-      <c r="A65" s="65" t="s">
+      <c r="E64" s="5"/>
+    </row>
+    <row r="65" s="61" customFormat="1" ht="45" spans="1:5">
+      <c r="A65" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C65" s="80" t="s">
+      <c r="C65" s="82" t="s">
         <v>95</v>
       </c>
-      <c r="D65" s="22" t="s">
+      <c r="D65" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="E65" s="22"/>
-    </row>
-    <row r="66" s="58" customFormat="1" ht="23.25" spans="1:5">
-      <c r="A66" s="86" t="s">
+      <c r="E65" s="24"/>
+    </row>
+    <row r="66" s="60" customFormat="1" ht="23.25" spans="1:5">
+      <c r="A66" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="B66" s="86"/>
-      <c r="C66" s="86"/>
-      <c r="D66" s="86"/>
-      <c r="E66" s="86"/>
+      <c r="B66" s="88"/>
+      <c r="C66" s="88"/>
+      <c r="D66" s="88"/>
+      <c r="E66" s="88"/>
     </row>
     <row r="67" ht="90" spans="1:5">
-      <c r="A67" s="75" t="s">
+      <c r="A67" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="B67" s="54" t="s">
+      <c r="B67" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="C67" s="76" t="s">
+      <c r="C67" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="D67" s="76" t="s">
+      <c r="D67" s="78" t="s">
         <v>101</v>
       </c>
-      <c r="E67" s="54"/>
+      <c r="E67" s="56"/>
     </row>
     <row r="68" ht="45" spans="1:5">
-      <c r="A68" s="75"/>
-      <c r="B68" s="3" t="s">
+      <c r="A68" s="77"/>
+      <c r="B68" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="66" t="s">
+      <c r="C68" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
     </row>
     <row r="69" ht="60" spans="1:5">
-      <c r="A69" s="77"/>
-      <c r="B69" s="3" t="s">
+      <c r="A69" s="79"/>
+      <c r="B69" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C69" s="66" t="s">
+      <c r="C69" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
     </row>
     <row r="70" ht="75" spans="1:5">
-      <c r="A70" s="67" t="s">
+      <c r="A70" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="66" t="s">
+      <c r="C70" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="D70" s="78" t="s">
+      <c r="D70" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="E70" s="3"/>
+      <c r="E70" s="5"/>
     </row>
     <row r="71" ht="45" spans="1:5">
-      <c r="A71" s="67" t="s">
+      <c r="A71" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -4726,356 +4698,278 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="35.1428571428571" customWidth="1"/>
-    <col min="2" max="2" width="40.8571428571429" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C1" t="s">
-        <v>305</v>
-      </c>
-      <c r="D1" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>316</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="42" style="38" customWidth="1"/>
-    <col min="2" max="2" width="46.3619047619048" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.952380952381" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.3714285714286" style="3" customWidth="1"/>
+    <col min="1" max="1" width="42" style="40" customWidth="1"/>
+    <col min="2" max="2" width="46.3619047619048" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.952380952381" style="5" customWidth="1"/>
+    <col min="4" max="4" width="13.3714285714286" style="5" customWidth="1"/>
     <col min="5" max="5" width="22.7238095238095" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:5">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:5">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:5">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="45">
         <v>16500000</v>
       </c>
-      <c r="D4" s="43">
+      <c r="D4" s="45">
         <v>16000000</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="26">
         <v>16000000</v>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1" spans="1:5">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="45">
         <v>4</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="45">
         <f>C5</f>
         <v>4</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="26">
         <f>D5</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:5">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="45">
         <v>200000</v>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="45">
         <v>400000</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="45">
         <v>500000</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:5">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="45">
         <v>26800</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="45">
         <v>52400</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="45">
         <v>65200</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="45">
         <f>C6-C7</f>
         <v>173200</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="45">
         <f>D6-D7</f>
         <v>347600</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="45">
         <f>E6-E7</f>
         <v>434800</v>
       </c>
     </row>
     <row r="9" ht="71" customHeight="1" spans="1:5">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="45">
         <f>3%*C8</f>
         <v>5196</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="45">
         <f>3%*D8</f>
         <v>10428</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="45">
         <f>3%*E8</f>
         <v>13044</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:5">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="45">
         <f>C8-C9</f>
         <v>168004</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="45">
         <f>D8-D9</f>
         <v>337172</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="45">
         <f>E8-E9</f>
         <v>421756</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:5">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="58">
         <f>15%*C4</f>
         <v>2475000</v>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="58">
         <f>15%*D4</f>
         <v>2400000</v>
       </c>
-      <c r="E11" s="56">
+      <c r="E11" s="58">
         <f>15%*E4</f>
         <v>2400000</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:5">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="45">
         <f>75%*C10</f>
         <v>126003</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="45">
         <f>75%*D10</f>
         <v>252879</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="45">
         <f>75%*E10</f>
         <v>316317</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="45">
         <f>C12</f>
         <v>126003</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="45">
         <f>D12</f>
         <v>252879</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="45">
         <f>E12</f>
         <v>316317</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:5">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43">
+      <c r="C14" s="45"/>
+      <c r="D14" s="45">
         <f>C15</f>
         <v>126003</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="45">
         <f>D15+C15</f>
         <v>252879</v>
       </c>
     </row>
     <row r="15" ht="33" customHeight="1" spans="1:5">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="59">
         <f>C13-C14</f>
         <v>126003</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="59">
         <f>D13-D14</f>
         <v>126876</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="59">
         <f>E13-E14</f>
         <v>63438</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5094,117 +4988,117 @@
   <dimension ref="A1:O12"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42" style="38" customWidth="1"/>
-    <col min="2" max="2" width="40" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.4952380952381" style="24" customWidth="1"/>
-    <col min="4" max="4" width="23.3714285714286" style="27" customWidth="1"/>
+    <col min="1" max="1" width="42" style="40" customWidth="1"/>
+    <col min="2" max="2" width="40" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.4952380952381" style="26" customWidth="1"/>
+    <col min="4" max="4" width="23.3714285714286" style="29" customWidth="1"/>
     <col min="5" max="5" width="24.8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:15">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:15">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:15">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="45">
         <v>5500001</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="26">
         <v>3000000</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="26">
         <v>9200001</v>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1" spans="1:15">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="45">
         <v>1</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="26">
         <f>C5</f>
         <v>1</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="26">
         <f>D5</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:15">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="45">
         <v>1100500</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="26">
         <v>1100000</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="26">
         <v>1800000</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:15">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="45">
         <v>3800</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="26">
         <v>1200</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="26">
         <v>20800</v>
       </c>
-      <c r="L7" s="45">
+      <c r="L7" s="47">
         <v>15000</v>
       </c>
       <c r="N7">
@@ -5212,21 +5106,21 @@
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:15">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="45">
         <f>C6-C7</f>
         <v>1096700</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="26">
         <f>D6-D7</f>
         <v>1098800</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="26">
         <f>E6-E7</f>
         <v>1779200</v>
       </c>
@@ -5241,62 +5135,62 @@
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:15">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="48">
         <f>75%*C8</f>
         <v>822525</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="48">
         <f>75%*D8</f>
         <v>824100</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="48">
         <f>75%*E8</f>
         <v>1334400</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:15">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="45">
         <v>0</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="26">
         <f>C11</f>
         <v>822525</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="26">
         <f>D11+C11</f>
         <v>824100</v>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1" spans="1:15">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="45">
         <f>C9-C10</f>
         <v>822525</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="49">
         <f>D9-D10</f>
         <v>1575</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="7">
         <f>E9-E10</f>
         <v>510300</v>
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="55"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5315,118 +5209,118 @@
   <dimension ref="A1:O19"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42" style="38" customWidth="1"/>
-    <col min="2" max="2" width="40" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.4952380952381" style="24" customWidth="1"/>
-    <col min="4" max="4" width="23.3714285714286" style="27" customWidth="1"/>
+    <col min="1" max="1" width="42" style="40" customWidth="1"/>
+    <col min="2" max="2" width="40" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.4952380952381" style="26" customWidth="1"/>
+    <col min="4" max="4" width="23.3714285714286" style="29" customWidth="1"/>
     <col min="5" max="5" width="24.8" customWidth="1"/>
     <col min="9" max="9" width="20.647619047619" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:15">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="42"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:15">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="42"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
     </row>
     <row r="4" ht="64" customHeight="1" spans="1:15">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="45">
         <v>5500001</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="26">
         <v>3000000</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="26">
         <v>9200001</v>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1" spans="1:15">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="45">
         <v>1</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="26">
         <f>C5</f>
         <v>1</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="26">
         <f>D5</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:15">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="45">
         <v>1100500</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="26">
         <v>1100000</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="26">
         <v>1800000</v>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1" spans="1:15">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="45">
         <v>3800</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="26">
         <v>1200</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="26">
         <v>20800</v>
       </c>
-      <c r="L7" s="45">
+      <c r="L7" s="47">
         <v>15000</v>
       </c>
       <c r="N7">
@@ -5434,21 +5328,21 @@
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:15">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="45">
         <f>C6-C7</f>
         <v>1096700</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="26">
         <f>D6-D7</f>
         <v>1098800</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="26">
         <f>E6-E7</f>
         <v>1779200</v>
       </c>
@@ -5463,131 +5357,131 @@
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:15">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="48">
         <f>75%*C8</f>
         <v>822525</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="48">
         <f>75%*D8</f>
         <v>824100</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="48">
         <f>75%*E8</f>
         <v>1334400</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:15">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="45">
         <v>0</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="26">
         <f>C11</f>
         <v>822525</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="26">
         <f>D11+C11</f>
         <v>824100</v>
       </c>
     </row>
     <row r="11" ht="125" customHeight="1" spans="1:15">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="45">
         <f>C9-C10</f>
         <v>822525</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="49">
         <f>D9-D10</f>
         <v>1575</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="7">
         <f>E9-E10</f>
         <v>510300</v>
       </c>
-      <c r="I11" s="48" t="s">
+      <c r="I11" s="50" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="51">
+      <c r="B12" s="52"/>
+      <c r="C12" s="53">
         <v>3000000</v>
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="5">
+      <c r="B13" s="31"/>
+      <c r="C13" s="7">
         <v>2680800</v>
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="5">
+      <c r="B14" s="31"/>
+      <c r="C14" s="7">
         <f>C13</f>
         <v>2680800</v>
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="5">
+      <c r="B15" s="31"/>
+      <c r="C15" s="7">
         <f>75%*C14</f>
         <v>2010600</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="5">
+      <c r="B16" s="31"/>
+      <c r="C16" s="7">
         <f>15%*C12</f>
         <v>450000</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="52"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="5" t="b">
+      <c r="A17" s="54"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="7" t="b">
         <f>IF(C15&gt;C16,C16=C15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="5">
+      <c r="B18" s="31"/>
+      <c r="C18" s="7">
         <f>15%*C14</f>
         <v>402120</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="52"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="5"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5617,199 +5511,199 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" s="32" customFormat="1" spans="1:14">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+    </row>
+    <row r="2" s="34" customFormat="1" spans="1:14">
+      <c r="A2" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="N2" s="32">
+      <c r="N2" s="34">
         <v>832.88</v>
       </c>
     </row>
-    <row r="3" s="32" customFormat="1" spans="1:14">
-      <c r="A3" s="34">
+    <row r="3" s="34" customFormat="1" spans="1:14">
+      <c r="A3" s="36">
         <v>48670</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="36">
         <v>49034</v>
       </c>
-      <c r="C3" s="35">
+      <c r="C3" s="37">
         <f>B3-A3+1</f>
         <v>365</v>
       </c>
-      <c r="D3" s="36">
+      <c r="D3" s="38">
         <f>1%*E3*C3/365</f>
         <v>1000</v>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="37">
         <v>100000</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="37">
         <f>D3*18%</f>
         <v>180</v>
       </c>
-      <c r="G3" s="35">
+      <c r="G3" s="37">
         <f>D3+F3</f>
         <v>1180</v>
       </c>
     </row>
-    <row r="4" s="32" customFormat="1"/>
+    <row r="4" s="34" customFormat="1"/>
     <row r="7" spans="1:14">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="35" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="34">
+      <c r="A9" s="36">
         <v>46072</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="36">
         <v>46112</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="37">
         <f>B9-A9+1</f>
         <v>41</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="38">
         <f>0.25%*E9*C9/365</f>
         <v>28.0821917808219</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="37">
         <v>100000</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="37">
         <f>D9*18%</f>
         <v>5.05479452054795</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="37">
         <f>D9+F9</f>
         <v>33.1369863013699</v>
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="F14" s="33" t="s">
+      <c r="F14" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="G14" s="33" t="s">
+      <c r="G14" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="H14" s="33" t="s">
+      <c r="H14" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="J14" s="33" t="s">
+      <c r="J14" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="35" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="37">
         <v>10000</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="36">
         <v>47209</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="36">
         <v>47573</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="37">
         <f>DATEDIF(C15,D15,"d")+1</f>
         <v>365</v>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="39">
         <v>0.005</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="37">
         <f>IF(K15="Closed",0,B15*F15*(E15/365))</f>
         <v>50</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="37">
         <f>G15*9%</f>
         <v>4.5</v>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="37">
         <f>18%*G15</f>
         <v>9</v>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="37">
         <f>G15+H15+I15</f>
         <v>63.5</v>
       </c>
-      <c r="K15" s="35" t="s">
+      <c r="K15" s="37" t="s">
         <v>160</v>
       </c>
     </row>
@@ -5845,559 +5739,559 @@
       </c>
     </row>
     <row r="2" spans="3:10">
-      <c r="C2" s="22"/>
-      <c r="D2" s="22" t="s">
+      <c r="C2" s="24"/>
+      <c r="D2" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="25" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="3" spans="3:10">
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25" t="s">
+      <c r="G3" s="27"/>
+      <c r="H3" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="J3" s="23"/>
+      <c r="J3" s="25"/>
     </row>
     <row r="4" spans="3:10">
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="G4" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="28">
         <v>46386</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="J4" s="23"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="3:10">
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="G5" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="28">
         <v>46477</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="J5" s="23"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" spans="3:10">
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="28">
         <v>46568</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="J6" s="23"/>
+      <c r="J6" s="25"/>
     </row>
     <row r="7" spans="3:10">
-      <c r="C7" s="27"/>
-      <c r="I7" s="27"/>
+      <c r="C7" s="29"/>
+      <c r="I7" s="29"/>
     </row>
     <row r="8" spans="3:10">
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="30">
         <v>46843</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="29" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="9" spans="3:10">
-      <c r="C9" s="27"/>
-      <c r="F9" s="29" t="s">
+      <c r="C9" s="29"/>
+      <c r="F9" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="G9" s="30" t="s">
+      <c r="G9" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="32">
         <v>46843</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="33" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="10" spans="3:10">
-      <c r="C10" s="27"/>
-      <c r="F10" s="29" t="s">
+      <c r="C10" s="29"/>
+      <c r="F10" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30">
+      <c r="G10" s="32"/>
+      <c r="H10" s="32">
         <v>46844</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="33" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="11" spans="3:10">
-      <c r="C11" s="27"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="27"/>
+      <c r="C11" s="29"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="29"/>
     </row>
     <row r="12" spans="3:10">
-      <c r="C12" s="27"/>
-      <c r="I12" s="27"/>
+      <c r="C12" s="29"/>
+      <c r="I12" s="29"/>
     </row>
     <row r="13" spans="3:10">
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="30">
         <v>47208</v>
       </c>
-      <c r="I13" s="24" t="s">
+      <c r="I13" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="J13" s="27" t="s">
+      <c r="J13" s="29" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="14" spans="3:10">
-      <c r="C14" s="27"/>
-      <c r="F14" s="29" t="s">
+      <c r="C14" s="29"/>
+      <c r="F14" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="32">
         <v>47208</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J14" s="31" t="s">
+      <c r="J14" s="33" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="15" spans="3:10">
-      <c r="C15" s="27"/>
-      <c r="F15" s="29" t="s">
+      <c r="C15" s="29"/>
+      <c r="F15" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30">
+      <c r="G15" s="32"/>
+      <c r="H15" s="32">
         <v>47209</v>
       </c>
-      <c r="I15" s="31" t="s">
+      <c r="I15" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J15" s="31" t="s">
+      <c r="J15" s="33" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="16" spans="3:10">
-      <c r="C16" s="27"/>
-      <c r="I16" s="27"/>
+      <c r="C16" s="29"/>
+      <c r="I16" s="29"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="27"/>
-      <c r="I17" s="27"/>
+      <c r="C17" s="29"/>
+      <c r="I17" s="29"/>
     </row>
     <row r="18" spans="3:10">
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="30">
         <v>47573</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="I18" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="J18" s="27" t="s">
+      <c r="J18" s="29" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="19" spans="3:10">
-      <c r="C19" s="27"/>
-      <c r="F19" s="29" t="s">
+      <c r="C19" s="29"/>
+      <c r="F19" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="G19" s="30" t="s">
+      <c r="G19" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="32">
         <v>47573</v>
       </c>
-      <c r="I19" s="31" t="s">
+      <c r="I19" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J19" s="31" t="s">
+      <c r="J19" s="33" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="20" spans="3:10">
-      <c r="C20" s="27"/>
-      <c r="F20" s="29" t="s">
+      <c r="C20" s="29"/>
+      <c r="F20" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30">
+      <c r="G20" s="32"/>
+      <c r="H20" s="32">
         <v>47574</v>
       </c>
-      <c r="I20" s="31" t="s">
+      <c r="I20" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J20" s="31" t="s">
+      <c r="J20" s="33" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="21" spans="3:10">
-      <c r="C21" s="27"/>
-      <c r="I21" s="27"/>
+      <c r="C21" s="29"/>
+      <c r="I21" s="29"/>
     </row>
     <row r="22" spans="3:10">
-      <c r="C22" s="27"/>
-      <c r="I22" s="27"/>
+      <c r="C22" s="29"/>
+      <c r="I22" s="29"/>
     </row>
     <row r="23" spans="3:10">
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G23" s="28" t="s">
+      <c r="G23" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="30">
         <v>47938</v>
       </c>
-      <c r="I23" s="24" t="s">
+      <c r="I23" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="J23" s="27" t="s">
+      <c r="J23" s="29" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="24" spans="3:10">
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="G24" s="30" t="s">
+      <c r="G24" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="32">
         <v>47938</v>
       </c>
-      <c r="I24" s="31" t="s">
+      <c r="I24" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J24" s="31" t="s">
+      <c r="J24" s="33" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="25" spans="3:10">
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30">
+      <c r="G25" s="32"/>
+      <c r="H25" s="32">
         <v>47939</v>
       </c>
-      <c r="I25" s="31" t="s">
+      <c r="I25" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J25" s="31" t="s">
+      <c r="J25" s="33" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="26" spans="3:10">
-      <c r="I26" s="27"/>
+      <c r="I26" s="29"/>
     </row>
     <row r="27" spans="3:10">
-      <c r="I27" s="27"/>
+      <c r="I27" s="29"/>
     </row>
     <row r="28" spans="3:10">
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G28" s="28" t="s">
+      <c r="G28" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="30">
         <v>48304</v>
       </c>
-      <c r="I28" s="24" t="s">
+      <c r="I28" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="J28" s="27" t="s">
+      <c r="J28" s="29" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="29" spans="3:10">
-      <c r="F29" s="29" t="s">
+      <c r="F29" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="G29" s="30" t="s">
+      <c r="G29" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="30">
+      <c r="H29" s="32">
         <v>48304</v>
       </c>
-      <c r="I29" s="31" t="s">
+      <c r="I29" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J29" s="31" t="s">
+      <c r="J29" s="33" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="30" spans="3:10">
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30">
+      <c r="G30" s="32"/>
+      <c r="H30" s="32">
         <v>48305</v>
       </c>
-      <c r="I30" s="31" t="s">
+      <c r="I30" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J30" s="31" t="s">
+      <c r="J30" s="33" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="31" spans="3:10">
-      <c r="I31" s="27"/>
+      <c r="I31" s="29"/>
     </row>
     <row r="32" spans="3:10">
-      <c r="I32" s="27"/>
+      <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:10">
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G33" s="28" t="s">
+      <c r="G33" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="H33" s="28">
+      <c r="H33" s="30">
         <v>48669</v>
       </c>
-      <c r="I33" s="24" t="s">
+      <c r="I33" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="J33" s="27" t="s">
+      <c r="J33" s="29" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="34" spans="3:10">
-      <c r="F34" s="29" t="s">
+      <c r="F34" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="G34" s="30" t="s">
+      <c r="G34" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="H34" s="30">
+      <c r="H34" s="32">
         <v>48669</v>
       </c>
-      <c r="I34" s="31" t="s">
+      <c r="I34" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J34" s="31" t="s">
+      <c r="J34" s="33" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="35" spans="3:10">
-      <c r="F35" s="29" t="s">
+      <c r="F35" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30">
+      <c r="G35" s="32"/>
+      <c r="H35" s="32">
         <v>48670</v>
       </c>
-      <c r="I35" s="31" t="s">
+      <c r="I35" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="J35" s="31" t="s">
+      <c r="J35" s="33" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="36" spans="3:10">
-      <c r="I36" s="27"/>
+      <c r="I36" s="29"/>
     </row>
     <row r="37" spans="3:10">
-      <c r="I37" s="27"/>
+      <c r="I37" s="29"/>
     </row>
     <row r="38" spans="3:10">
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="G38" s="28" t="s">
+      <c r="G38" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="H38" s="28">
+      <c r="H38" s="30">
         <v>49034</v>
       </c>
-      <c r="I38" s="24" t="s">
+      <c r="I38" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="J38" s="27" t="s">
+      <c r="J38" s="29" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="39" spans="3:10">
-      <c r="F39" s="29"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="31"/>
+      <c r="J39" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6428,787 +6322,787 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="9" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="11">
         <v>100000</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="9"/>
+      <c r="G2" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="11">
         <v>100000</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="13">
         <v>100000</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="13">
         <v>100000</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="13">
         <v>100000</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="13">
         <v>100000</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="13">
         <v>100000</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="13">
         <v>100000</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="13">
         <v>100000</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="13">
         <v>100000</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="13">
         <v>100000</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="13">
         <v>100000</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="13">
         <v>100000</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="13">
         <v>100000</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="13">
         <v>100000</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="13">
         <v>100000</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="13">
         <v>100000</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="13">
         <v>100000</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="13">
         <v>100000</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="16">
         <v>100000</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="16">
         <v>100000</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="16">
         <v>100000</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="18">
         <v>100000</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="18">
         <v>100000</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="11">
         <v>10000</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7" t="s">
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="20">
         <v>605501.57</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7" t="s">
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="11">
         <v>200000.56</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7" t="s">
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="23">
         <v>200000.56</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7" t="s">
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
@@ -7238,19 +7132,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="L1" s="3"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" ht="30" spans="2:12">
       <c r="B2" t="s">
@@ -7262,15 +7156,15 @@
       <c r="G2" t="s">
         <v>262</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
     </row>
     <row r="3" ht="30" spans="2:12">
       <c r="B3" t="s">
@@ -7282,34 +7176,34 @@
       <c r="D3" t="s">
         <v>223</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="5"/>
     </row>
     <row r="4" ht="30" spans="2:12">
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="5" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7323,118 +7217,118 @@
       <c r="D5" t="s">
         <v>274</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3" t="s">
+      <c r="K5" s="5"/>
+      <c r="L5" s="5" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="6" ht="45" spans="2:12">
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3" t="s">
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="7" ht="45" spans="2:12">
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="4" t="s">
+      <c r="K7" s="5"/>
+      <c r="L7" s="6" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="8" ht="60" spans="2:12">
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3" t="s">
+      <c r="K8" s="5"/>
+      <c r="L8" s="5" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="9" ht="60" spans="2:12">
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3" t="s">
+      <c r="K9" s="5"/>
+      <c r="L9" s="5" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="10" ht="60" spans="2:12">
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="4" t="s">
+      <c r="K10" s="5"/>
+      <c r="L10" s="6" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="11" ht="30" spans="2:12">
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="5" t="s">
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="7" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="12" ht="30" spans="2:12">
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="7"/>
     </row>
     <row r="17" spans="8:9">
       <c r="H17" t="s">
@@ -7442,34 +7336,34 @@
       </c>
     </row>
     <row r="19" spans="8:9">
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="5" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="20" spans="8:9">
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="5" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="21" spans="8:9">
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="5" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="22" spans="8:9">
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="5" t="s">
         <v>294</v>
       </c>
     </row>
@@ -7493,106 +7387,108 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <dimension ref="B2:F12"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="12.4285714285714" customWidth="1"/>
-    <col min="7" max="7" width="24.2857142857143" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="1" max="1" width="12.2857142857143" customWidth="1"/>
+    <col min="2" max="2" width="15.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="17.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="D1" t="s">
+    <row r="2" spans="2:6">
+      <c r="B2" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="B2" t="s">
+    <row r="3" spans="2:6">
+      <c r="B3" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="B3" t="s">
+      <c r="D7" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="B4" t="s">
+      <c r="D8" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C4" t="s">
-        <v>296</v>
-      </c>
-      <c r="D4" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="B5" t="s">
+      <c r="D9" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C5" t="s">
-        <v>296</v>
-      </c>
-      <c r="D5" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="B8" t="s">
+      <c r="D10" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="C12" t="s">
         <v>265</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="G15" s="1">
-        <f>15%*3000000</f>
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="17" spans="7:9">
-      <c r="G17" s="1">
-        <f>75%*2700000</f>
-        <v>2025000</v>
-      </c>
-      <c r="I17" t="s">
-        <v>136</v>
+      <c r="F12" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:E10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
